--- a/historico/historico.xlsx
+++ b/historico/historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -943,6 +943,21 @@
         <v>28</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Palestra Rock In Rio (respostas).xlsx</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>18/05/2026 10:53</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historico/historico.xlsx
+++ b/historico/historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,6 +958,21 @@
         <v>28</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Palestra Rock In Rio (respostas).xlsx</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>18/05/2026 11:03</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historico/historico.xlsx
+++ b/historico/historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -973,6 +973,21 @@
         <v>28</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Palestra Rock In Rio (respostas).xlsx</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>22/05/2026 11:58</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historico/historico.xlsx
+++ b/historico/historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -988,6 +988,36 @@
         <v>28</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Planilha_teste.xlsx</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>29/05/2026 10:04</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Planilha_teste.xlsx</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>29/05/2026 10:14</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historico/historico.xlsx
+++ b/historico/historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1018,6 +1018,36 @@
         <v>2</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Planilha_teste.xlsx</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>29/05/2026 10:21</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Planilha_teste.xlsx</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>29/05/2026 10:21</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historico/historico.xlsx
+++ b/historico/historico.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1048,6 +1048,36 @@
         <v>2</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Planilha_teste.xlsx</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>09/06/2026 19:49</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Planilha_teste.xlsx</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>09/06/2026 20:11</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
